--- a/data/b2_bonsucesso/B2 Bonsucesso 09-2026.xlsx
+++ b/data/b2_bonsucesso/B2 Bonsucesso 09-2026.xlsx
@@ -14,7 +14,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'MOVIMENTO DIÁRIO'!$A$1:$H$109</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'COMPRAS'!$A$1:$G$19</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'COMPRAS'!$A$1:$G$18</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'DESPESAS'!$A$1:$D$16</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -3737,7 +3737,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G19"/>
+  <dimension ref="A1:G18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3977,28 +3977,28 @@
     </row>
     <row r="9">
       <c r="A9" s="12" t="n">
-        <v>46277</v>
+        <v>46279</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Gasolina Comum</t>
+          <t>Gasolina Aditivada</t>
         </is>
       </c>
       <c r="C9" s="13" t="n">
-        <v>35000</v>
+        <v>10000</v>
       </c>
       <c r="D9" s="14" t="n">
-        <v>5.7605</v>
+        <v>5.8885</v>
       </c>
       <c r="E9" s="17" t="n">
-        <v>201617.45</v>
+        <v>58884.6</v>
       </c>
       <c r="F9" t="n">
-        <v>148785</v>
+        <v>148798</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Distribuidora Alfa</t>
+          <t>Distribuidora Paraná</t>
         </is>
       </c>
     </row>
@@ -4008,20 +4008,20 @@
       </c>
       <c r="B10" s="8" t="inlineStr">
         <is>
-          <t>Gasolina Aditivada</t>
+          <t>Diesel S10</t>
         </is>
       </c>
       <c r="C10" s="9" t="n">
-        <v>10000</v>
+        <v>15000</v>
       </c>
       <c r="D10" s="10" t="n">
-        <v>5.8885</v>
+        <v>5.8259</v>
       </c>
       <c r="E10" s="16" t="n">
-        <v>58884.6</v>
+        <v>87389.2</v>
       </c>
       <c r="F10" s="8" t="n">
-        <v>148798</v>
+        <v>148809</v>
       </c>
       <c r="G10" s="8" t="inlineStr">
         <is>
@@ -4031,82 +4031,82 @@
     </row>
     <row r="11">
       <c r="A11" s="12" t="n">
-        <v>46279</v>
+        <v>46281</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Diesel S10</t>
+          <t>Etanol</t>
         </is>
       </c>
       <c r="C11" s="13" t="n">
         <v>15000</v>
       </c>
       <c r="D11" s="14" t="n">
-        <v>5.8259</v>
+        <v>4</v>
       </c>
       <c r="E11" s="17" t="n">
-        <v>87389.2</v>
+        <v>59999.38</v>
       </c>
       <c r="F11" t="n">
-        <v>148809</v>
+        <v>148819</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Distribuidora Paraná</t>
+          <t>Distribuidora Alfa</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="7" t="n">
-        <v>46281</v>
+        <v>46284</v>
       </c>
       <c r="B12" s="8" t="inlineStr">
         <is>
-          <t>Etanol</t>
+          <t>Gasolina Comum</t>
         </is>
       </c>
       <c r="C12" s="9" t="n">
-        <v>15000</v>
+        <v>35000</v>
       </c>
       <c r="D12" s="10" t="n">
-        <v>4</v>
+        <v>5.751</v>
       </c>
       <c r="E12" s="16" t="n">
-        <v>59999.38</v>
+        <v>201284.47</v>
       </c>
       <c r="F12" s="8" t="n">
-        <v>148819</v>
+        <v>148822</v>
       </c>
       <c r="G12" s="8" t="inlineStr">
         <is>
-          <t>Distribuidora Alfa</t>
+          <t>Distribuidora Paraná</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="12" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Gasolina Comum</t>
+          <t>Gasolina Aditivada</t>
         </is>
       </c>
       <c r="C13" s="13" t="n">
-        <v>35000</v>
+        <v>10000</v>
       </c>
       <c r="D13" s="14" t="n">
-        <v>5.751</v>
+        <v>5.9105</v>
       </c>
       <c r="E13" s="17" t="n">
-        <v>201284.47</v>
+        <v>59105.2</v>
       </c>
       <c r="F13" t="n">
-        <v>148822</v>
+        <v>148844</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Distribuidora Paraná</t>
+          <t>Distribuidora Alfa</t>
         </is>
       </c>
     </row>
@@ -4116,24 +4116,24 @@
       </c>
       <c r="B14" s="8" t="inlineStr">
         <is>
-          <t>Gasolina Aditivada</t>
+          <t>Etanol</t>
         </is>
       </c>
       <c r="C14" s="9" t="n">
-        <v>10000</v>
+        <v>15000</v>
       </c>
       <c r="D14" s="10" t="n">
-        <v>5.9105</v>
+        <v>4.0124</v>
       </c>
       <c r="E14" s="16" t="n">
-        <v>59105.2</v>
+        <v>60186.51</v>
       </c>
       <c r="F14" s="8" t="n">
-        <v>148844</v>
+        <v>148878</v>
       </c>
       <c r="G14" s="8" t="inlineStr">
         <is>
-          <t>Distribuidora Alfa</t>
+          <t>Distribuidora Sul</t>
         </is>
       </c>
     </row>
@@ -4143,47 +4143,47 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Etanol</t>
+          <t>Diesel S10</t>
         </is>
       </c>
       <c r="C15" s="13" t="n">
         <v>15000</v>
       </c>
       <c r="D15" s="14" t="n">
-        <v>4.0124</v>
+        <v>6.1013</v>
       </c>
       <c r="E15" s="17" t="n">
-        <v>60186.51</v>
+        <v>91519.87</v>
       </c>
       <c r="F15" t="n">
-        <v>148878</v>
+        <v>148896</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Distribuidora Sul</t>
+          <t>Distribuidora Paraná</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="7" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="B16" s="8" t="inlineStr">
         <is>
-          <t>Diesel S10</t>
+          <t>Gasolina Comum</t>
         </is>
       </c>
       <c r="C16" s="9" t="n">
-        <v>15000</v>
+        <v>25000</v>
       </c>
       <c r="D16" s="10" t="n">
-        <v>6.1013</v>
+        <v>5.7495</v>
       </c>
       <c r="E16" s="16" t="n">
-        <v>91519.87</v>
+        <v>143736.27</v>
       </c>
       <c r="F16" s="8" t="n">
-        <v>148896</v>
+        <v>148905</v>
       </c>
       <c r="G16" s="8" t="inlineStr">
         <is>
@@ -4193,51 +4193,51 @@
     </row>
     <row r="17">
       <c r="A17" s="12" t="n">
-        <v>46288</v>
+        <v>46290</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Gasolina Comum</t>
+          <t>Diesel S10</t>
         </is>
       </c>
       <c r="C17" s="13" t="n">
-        <v>25000</v>
+        <v>15000</v>
       </c>
       <c r="D17" s="14" t="n">
-        <v>5.7495</v>
+        <v>6.1086</v>
       </c>
       <c r="E17" s="17" t="n">
-        <v>143736.27</v>
+        <v>91629.05</v>
       </c>
       <c r="F17" t="n">
-        <v>148905</v>
+        <v>148937</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Distribuidora Paraná</t>
+          <t>Distribuidora Alfa</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="7" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="B18" s="8" t="inlineStr">
         <is>
-          <t>Diesel S10</t>
+          <t>Etanol</t>
         </is>
       </c>
       <c r="C18" s="9" t="n">
         <v>15000</v>
       </c>
       <c r="D18" s="10" t="n">
-        <v>6.1086</v>
+        <v>3.9914</v>
       </c>
       <c r="E18" s="16" t="n">
-        <v>91629.05</v>
+        <v>59871.34</v>
       </c>
       <c r="F18" s="8" t="n">
-        <v>148937</v>
+        <v>148973</v>
       </c>
       <c r="G18" s="8" t="inlineStr">
         <is>
@@ -4245,35 +4245,8 @@
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="12" t="n">
-        <v>46291</v>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Etanol</t>
-        </is>
-      </c>
-      <c r="C19" s="13" t="n">
-        <v>15000</v>
-      </c>
-      <c r="D19" s="14" t="n">
-        <v>3.9914</v>
-      </c>
-      <c r="E19" s="17" t="n">
-        <v>59871.34</v>
-      </c>
-      <c r="F19" t="n">
-        <v>148973</v>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>Distribuidora Alfa</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:G19"/>
+  <autoFilter ref="A1:G18"/>
   <dataValidations count="1">
     <dataValidation sqref="B2:B2000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Valor fora da lista" error="Escolha um item da lista." type="list">
       <formula1>"Gasolina Comum,Gasolina Aditivada,Etanol,Diesel S10"</formula1>

--- a/data/b2_bonsucesso/B2 Bonsucesso 09-2026.xlsx
+++ b/data/b2_bonsucesso/B2 Bonsucesso 09-2026.xlsx
@@ -13,9 +13,9 @@
     <sheet name="DESPESAS" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'MOVIMENTO DIÁRIO'!$A$1:$H$109</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'COMPRAS'!$A$1:$G$18</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'DESPESAS'!$A$1:$D$16</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'MOVIMENTO DIÁRIO'!$A$1:$H$121</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'COMPRAS'!$A$1:$G$21</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'DESPESAS'!$A$1:$D$17</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -641,7 +641,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H109"/>
+  <dimension ref="A1:H121"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3720,8 +3720,344 @@
         <v>6.384</v>
       </c>
     </row>
+    <row r="110">
+      <c r="A110" s="7" t="n">
+        <v>46293</v>
+      </c>
+      <c r="B110" s="8" t="inlineStr">
+        <is>
+          <t>Gasolina Comum</t>
+        </is>
+      </c>
+      <c r="C110" s="9" t="n">
+        <v>24268</v>
+      </c>
+      <c r="D110" s="9" t="n">
+        <v>30000</v>
+      </c>
+      <c r="E110" s="9" t="n">
+        <v>5676</v>
+      </c>
+      <c r="F110" s="9" t="n">
+        <v>48589</v>
+      </c>
+      <c r="G110" s="10" t="n">
+        <v>5.768</v>
+      </c>
+      <c r="H110" s="11" t="n">
+        <v>6.389</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="12" t="n">
+        <v>46293</v>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>Gasolina Aditivada</t>
+        </is>
+      </c>
+      <c r="C111" s="13" t="n">
+        <v>4739</v>
+      </c>
+      <c r="D111" s="13" t="n">
+        <v>10000</v>
+      </c>
+      <c r="E111" s="13" t="n">
+        <v>1519</v>
+      </c>
+      <c r="F111" s="13" t="n">
+        <v>13218</v>
+      </c>
+      <c r="G111" s="14" t="n">
+        <v>5.8912</v>
+      </c>
+      <c r="H111" s="15" t="n">
+        <v>6.788</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="7" t="n">
+        <v>46293</v>
+      </c>
+      <c r="B112" s="8" t="inlineStr">
+        <is>
+          <t>Etanol</t>
+        </is>
+      </c>
+      <c r="C112" s="9" t="n">
+        <v>21198</v>
+      </c>
+      <c r="D112" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E112" s="9" t="n">
+        <v>2798</v>
+      </c>
+      <c r="F112" s="9" t="n">
+        <v>18399</v>
+      </c>
+      <c r="G112" s="10" t="n">
+        <v>3.9968</v>
+      </c>
+      <c r="H112" s="11" t="n">
+        <v>4.48</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="12" t="n">
+        <v>46293</v>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>Diesel S10</t>
+        </is>
+      </c>
+      <c r="C113" s="13" t="n">
+        <v>19593</v>
+      </c>
+      <c r="D113" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E113" s="13" t="n">
+        <v>2613</v>
+      </c>
+      <c r="F113" s="13" t="n">
+        <v>16977</v>
+      </c>
+      <c r="G113" s="14" t="n">
+        <v>6.0582</v>
+      </c>
+      <c r="H113" s="15" t="n">
+        <v>6.389</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="7" t="n">
+        <v>46294</v>
+      </c>
+      <c r="B114" s="8" t="inlineStr">
+        <is>
+          <t>Gasolina Comum</t>
+        </is>
+      </c>
+      <c r="C114" s="9" t="n">
+        <v>48589</v>
+      </c>
+      <c r="D114" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E114" s="9" t="n">
+        <v>4401</v>
+      </c>
+      <c r="F114" s="9" t="n">
+        <v>44179</v>
+      </c>
+      <c r="G114" s="10" t="n">
+        <v>5.768</v>
+      </c>
+      <c r="H114" s="11" t="n">
+        <v>6.39</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="12" t="n">
+        <v>46294</v>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>Gasolina Aditivada</t>
+        </is>
+      </c>
+      <c r="C115" s="13" t="n">
+        <v>13218</v>
+      </c>
+      <c r="D115" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E115" s="13" t="n">
+        <v>1423</v>
+      </c>
+      <c r="F115" s="13" t="n">
+        <v>11791</v>
+      </c>
+      <c r="G115" s="14" t="n">
+        <v>5.8912</v>
+      </c>
+      <c r="H115" s="15" t="n">
+        <v>6.784</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="7" t="n">
+        <v>46294</v>
+      </c>
+      <c r="B116" s="8" t="inlineStr">
+        <is>
+          <t>Etanol</t>
+        </is>
+      </c>
+      <c r="C116" s="9" t="n">
+        <v>18399</v>
+      </c>
+      <c r="D116" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E116" s="9" t="n">
+        <v>2516</v>
+      </c>
+      <c r="F116" s="9" t="n">
+        <v>15879</v>
+      </c>
+      <c r="G116" s="10" t="n">
+        <v>3.9968</v>
+      </c>
+      <c r="H116" s="11" t="n">
+        <v>4.482</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="12" t="n">
+        <v>46294</v>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>Diesel S10</t>
+        </is>
+      </c>
+      <c r="C117" s="13" t="n">
+        <v>16977</v>
+      </c>
+      <c r="D117" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E117" s="13" t="n">
+        <v>2450</v>
+      </c>
+      <c r="F117" s="13" t="n">
+        <v>14524</v>
+      </c>
+      <c r="G117" s="14" t="n">
+        <v>6.0582</v>
+      </c>
+      <c r="H117" s="15" t="n">
+        <v>6.381</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="7" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B118" s="8" t="inlineStr">
+        <is>
+          <t>Gasolina Comum</t>
+        </is>
+      </c>
+      <c r="C118" s="9" t="n">
+        <v>44179</v>
+      </c>
+      <c r="D118" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E118" s="9" t="n">
+        <v>5946</v>
+      </c>
+      <c r="F118" s="9" t="n">
+        <v>38231</v>
+      </c>
+      <c r="G118" s="10" t="n">
+        <v>5.768</v>
+      </c>
+      <c r="H118" s="11" t="n">
+        <v>6.387</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="12" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Gasolina Aditivada</t>
+        </is>
+      </c>
+      <c r="C119" s="13" t="n">
+        <v>11791</v>
+      </c>
+      <c r="D119" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E119" s="13" t="n">
+        <v>1436</v>
+      </c>
+      <c r="F119" s="13" t="n">
+        <v>10350</v>
+      </c>
+      <c r="G119" s="14" t="n">
+        <v>5.8912</v>
+      </c>
+      <c r="H119" s="15" t="n">
+        <v>6.782</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="7" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B120" s="8" t="inlineStr">
+        <is>
+          <t>Etanol</t>
+        </is>
+      </c>
+      <c r="C120" s="9" t="n">
+        <v>15879</v>
+      </c>
+      <c r="D120" s="9" t="n">
+        <v>10000</v>
+      </c>
+      <c r="E120" s="9" t="n">
+        <v>2806</v>
+      </c>
+      <c r="F120" s="9" t="n">
+        <v>23075</v>
+      </c>
+      <c r="G120" s="10" t="n">
+        <v>3.9935</v>
+      </c>
+      <c r="H120" s="11" t="n">
+        <v>4.484</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="12" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>Diesel S10</t>
+        </is>
+      </c>
+      <c r="C121" s="13" t="n">
+        <v>14524</v>
+      </c>
+      <c r="D121" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E121" s="13" t="n">
+        <v>2880</v>
+      </c>
+      <c r="F121" s="13" t="n">
+        <v>11641</v>
+      </c>
+      <c r="G121" s="14" t="n">
+        <v>6.0582</v>
+      </c>
+      <c r="H121" s="15" t="n">
+        <v>6.386</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H109"/>
+  <autoFilter ref="A1:H121"/>
   <dataValidations count="1">
     <dataValidation sqref="B2:B2000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Valor fora da lista" error="Escolha um item da lista." type="list">
       <formula1>"Gasolina Comum,Gasolina Aditivada,Etanol,Diesel S10"</formula1>
@@ -3737,7 +4073,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G18"/>
+  <dimension ref="A1:G21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4245,8 +4581,89 @@
         </is>
       </c>
     </row>
+    <row r="19">
+      <c r="A19" s="12" t="n">
+        <v>46293</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Gasolina Comum</t>
+        </is>
+      </c>
+      <c r="C19" s="13" t="n">
+        <v>30000</v>
+      </c>
+      <c r="D19" s="14" t="n">
+        <v>5.7795</v>
+      </c>
+      <c r="E19" s="17" t="n">
+        <v>173383.84</v>
+      </c>
+      <c r="F19" t="n">
+        <v>149000</v>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Distribuidora Sul</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="7" t="n">
+        <v>46293</v>
+      </c>
+      <c r="B20" s="8" t="inlineStr">
+        <is>
+          <t>Gasolina Aditivada</t>
+        </is>
+      </c>
+      <c r="C20" s="9" t="n">
+        <v>10000</v>
+      </c>
+      <c r="D20" s="10" t="n">
+        <v>5.8835</v>
+      </c>
+      <c r="E20" s="16" t="n">
+        <v>58834.68</v>
+      </c>
+      <c r="F20" s="8" t="n">
+        <v>149009</v>
+      </c>
+      <c r="G20" s="8" t="inlineStr">
+        <is>
+          <t>Distribuidora Paraná</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="12" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Etanol</t>
+        </is>
+      </c>
+      <c r="C21" s="13" t="n">
+        <v>10000</v>
+      </c>
+      <c r="D21" s="14" t="n">
+        <v>3.9883</v>
+      </c>
+      <c r="E21" s="17" t="n">
+        <v>39883.02</v>
+      </c>
+      <c r="F21" t="n">
+        <v>149025</v>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Distribuidora Alfa</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G18"/>
+  <autoFilter ref="A1:G21"/>
   <dataValidations count="1">
     <dataValidation sqref="B2:B2000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Valor fora da lista" error="Escolha um item da lista." type="list">
       <formula1>"Gasolina Comum,Gasolina Aditivada,Etanol,Diesel S10"</formula1>
@@ -4262,7 +4679,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D16"/>
+  <dimension ref="A1:D17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4295,218 +4712,218 @@
     </row>
     <row r="2">
       <c r="A2" s="7" t="n">
-        <v>46270</v>
+        <v>46269</v>
       </c>
       <c r="B2" s="8" t="inlineStr">
         <is>
-          <t>Folha de pagamento</t>
+          <t>Outras despesas</t>
         </is>
       </c>
       <c r="C2" s="8" t="inlineStr">
         <is>
-          <t>Salários do mês anterior</t>
+          <t>Material de limpeza e escritório</t>
         </is>
       </c>
       <c r="D2" s="16" t="n">
-        <v>65211.72</v>
+        <v>1137.87</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="12" t="n">
-        <v>46271</v>
+        <v>46269</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Taxas de cartão</t>
+          <t>Outras despesas</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Taxas das maquininhas (semana)</t>
+          <t>Coleta de resíduos (óleo e borra)</t>
         </is>
       </c>
       <c r="D3" s="17" t="n">
-        <v>4007.37</v>
+        <v>1191.94</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="7" t="n">
-        <v>46275</v>
+        <v>46270</v>
       </c>
       <c r="B4" s="8" t="inlineStr">
         <is>
-          <t>Outras despesas</t>
+          <t>Folha de pagamento</t>
         </is>
       </c>
       <c r="C4" s="8" t="inlineStr">
         <is>
-          <t>Tarifas bancárias</t>
+          <t>Salários do mês anterior</t>
         </is>
       </c>
       <c r="D4" s="16" t="n">
-        <v>1347.96</v>
+        <v>66075.78999999999</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="12" t="n">
-        <v>46275</v>
+        <v>46271</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Sistemas e contabilidade</t>
+          <t>Taxas de cartão</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Sistema de automação e contabilidade</t>
+          <t>Taxas das maquininhas (semana)</t>
         </is>
       </c>
       <c r="D5" s="17" t="n">
-        <v>3600</v>
+        <v>3910.34</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="n">
-        <v>46276</v>
+        <v>46275</v>
       </c>
       <c r="B6" s="8" t="inlineStr">
         <is>
-          <t>Outras despesas</t>
+          <t>Manutenção</t>
         </is>
       </c>
       <c r="C6" s="8" t="inlineStr">
         <is>
-          <t>Coleta de resíduos (óleo e borra)</t>
+          <t>Manutenção do compressor de ar</t>
         </is>
       </c>
       <c r="D6" s="16" t="n">
-        <v>1825.26</v>
+        <v>2824.2</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="12" t="n">
-        <v>46277</v>
+        <v>46275</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Água e esgoto</t>
+          <t>Sistemas e contabilidade</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Conta de água</t>
+          <t>Sistema de automação e contabilidade</t>
         </is>
       </c>
       <c r="D7" s="17" t="n">
-        <v>1362.18</v>
+        <v>3600</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="7" t="n">
-        <v>46278</v>
+        <v>46277</v>
       </c>
       <c r="B8" s="8" t="inlineStr">
         <is>
-          <t>Taxas de cartão</t>
+          <t>Manutenção</t>
         </is>
       </c>
       <c r="C8" s="8" t="inlineStr">
         <is>
-          <t>Taxas das maquininhas (semana)</t>
+          <t>Reparo elétrico</t>
         </is>
       </c>
       <c r="D8" s="16" t="n">
-        <v>4311.14</v>
+        <v>2508.48</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="12" t="n">
-        <v>46280</v>
+        <v>46277</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Energia elétrica</t>
+          <t>Água e esgoto</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Conta de energia</t>
+          <t>Conta de água</t>
         </is>
       </c>
       <c r="D9" s="17" t="n">
-        <v>9782.370000000001</v>
+        <v>1369.61</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="n">
-        <v>46280</v>
+        <v>46278</v>
       </c>
       <c r="B10" s="8" t="inlineStr">
         <is>
-          <t>Marketing</t>
+          <t>Outras despesas</t>
         </is>
       </c>
       <c r="C10" s="8" t="inlineStr">
         <is>
-          <t>Placas, redes sociais e brindes</t>
+          <t>Monitoramento e alarme</t>
         </is>
       </c>
       <c r="D10" s="16" t="n">
-        <v>1842.63</v>
+        <v>2046.67</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="12" t="n">
-        <v>46280</v>
+        <v>46278</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Outras despesas</t>
+          <t>Taxas de cartão</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Material de limpeza e escritório</t>
+          <t>Taxas das maquininhas (semana)</t>
         </is>
       </c>
       <c r="D11" s="17" t="n">
-        <v>1174.93</v>
+        <v>4622.64</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="7" t="n">
-        <v>46281</v>
+        <v>46280</v>
       </c>
       <c r="B12" s="8" t="inlineStr">
         <is>
-          <t>Manutenção</t>
+          <t>Energia elétrica</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
         <is>
-          <t>Troca de filtros das bombas</t>
+          <t>Conta de energia</t>
         </is>
       </c>
       <c r="D12" s="16" t="n">
-        <v>1531.85</v>
+        <v>10582.37</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="12" t="n">
-        <v>46282</v>
+        <v>46280</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Manutenção</t>
+          <t>Marketing</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Reparo elétrico</t>
+          <t>Placas, redes sociais e brindes</t>
         </is>
       </c>
       <c r="D13" s="17" t="n">
-        <v>1974.21</v>
+        <v>2161.24</v>
       </c>
     </row>
     <row r="14">
@@ -4524,7 +4941,7 @@
         </is>
       </c>
       <c r="D14" s="16" t="n">
-        <v>23263.25</v>
+        <v>22779.31</v>
       </c>
     </row>
     <row r="15">
@@ -4542,7 +4959,7 @@
         </is>
       </c>
       <c r="D15" s="17" t="n">
-        <v>4600.04</v>
+        <v>4106.8</v>
       </c>
     </row>
     <row r="16">
@@ -4560,11 +4977,29 @@
         </is>
       </c>
       <c r="D16" s="16" t="n">
-        <v>4597.76</v>
+        <v>4878.49</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="12" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Taxas de cartão</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Taxas das maquininhas (semana)</t>
+        </is>
+      </c>
+      <c r="D17" s="17" t="n">
+        <v>1747.49</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D16"/>
+  <autoFilter ref="A1:D17"/>
   <dataValidations count="1">
     <dataValidation sqref="B2:B2000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Valor fora da lista" error="Escolha um item da lista." type="list">
       <formula1>"Folha de pagamento,Aluguel,Energia elétrica,Água e esgoto,Taxas de cartão,Manutenção,Fretes,Sistemas e contabilidade,Marketing,Outras despesas"</formula1>
